--- a/important_mails_2026-05-09.xlsx
+++ b/important_mails_2026-05-09.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 9 May 2026 08:34:05 +0000</t>
+          <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -510,11 +510,62 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ca
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 9 May 2026 08:34:05 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -526,39 +577,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -570,39 +621,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -614,39 +665,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -670,39 +721,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -725,39 +776,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -777,39 +828,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -829,39 +880,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -881,39 +932,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -934,39 +985,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -986,39 +1037,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1038,39 +1089,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -1086,39 +1137,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1135,39 +1186,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1187,39 +1238,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1239,39 +1290,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1288,39 +1339,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -1335,39 +1386,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1380,58 +1431,6 @@
  Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
  Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
 Więcej o raportach płatności w S</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 15:23:38 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>跨账户负余额调整</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- 我们已于 五月 2, 2026使用您的 Amazon.es 账户中的可用资金调整了您的 Amazon.de 卖家账户上应付的 €69.53 的负余额。通过登录您的账户并导航至 付款控制面板 ，您可以随时查看您的账户余额。
-有关更多信息，请访问 跨账户负余额调整 。
-诚挚的问候！
-欧洲亚马逊 Payments
- 报告此电子邮件的问题
- 如有任何疑问，请访问： 卖家平台
- 要更改您的电子邮件首选项，请访问： 通知首选项
- 2026 Amazon, Inc. 或其附属公司。保留所有权利。
- 欧洲亚马逊 Payments S.C.A.（société en Commandite par actions），是一家在卢森堡注册的股份有限公司，注册号（RCS Luxembourg）B 153 265，公司总部位于 38 avenue J.F.Kennedy, L-1855 Luxembourg。增值税编号为 LU 24448288。
- 欧洲亚马逊 Payments S.C.A. 由卢森堡金融行业监管委员会授权，并由爱尔兰中央银行对其业务行为规则的遵守情况进行监管。
- 亚马逊 Payments 是欧洲亚马逊 Payments S.C.A. 的商业名称。
- 此电子邮件发送自不受监控的电子邮件地址。
- SPC-EUAmazon-1724035883551525</t>
         </is>
       </c>
     </row>
@@ -3140,21 +3139,73 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Fri, 1 May 2026 23:31:40 +0000</t>
+          <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>跨账户负余额调整</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ 我们已于 五月 2, 2026使用您的 Amazon.es 账户中的可用资金调整了您的 Amazon.de 卖家账户上应付的 €69.53 的负余额。通过登录您的账户并导航至 付款控制面板 ，您可以随时查看您的账户余额。
+有关更多信息，请访问 跨账户负余额调整 。
+诚挚的问候！
+欧洲亚马逊 Payments
+ 报告此电子邮件的问题
+ 如有任何疑问，请访问： 卖家平台
+ 要更改您的电子邮件首选项，请访问： 通知首选项
+ 2026 Amazon, Inc. 或其附属公司。保留所有权利。
+ 欧洲亚马逊 Payments S.C.A.（société en Commandite par actions），是一家在卢森堡注册的股份有限公司，注册号（RCS Luxembourg）B 153 265，公司总部位于 38 avenue J.F.Kennedy, L-1855 Luxembourg。增值税编号为 LU 24448288。
+ 欧洲亚马逊 Payments S.C.A. 由卢森堡金融行业监管委员会授权，并由爱尔兰中央银行对其业务行为规则的遵守情况进行监管。
+ 亚马逊 Payments 是欧洲亚马逊 Payments S.C.A. 的商业名称。
+ 此电子邮件发送自不受监控的电子邮件地址。
+ SPC-EUAmazon-1724035883551525</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 1 May 2026 23:31:40 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3174,39 +3225,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3223,39 +3274,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3275,39 +3326,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3327,39 +3378,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3376,39 +3427,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3428,39 +3479,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3474,39 +3525,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3526,39 +3577,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3575,39 +3626,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3623,39 +3674,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3675,39 +3726,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3724,39 +3775,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3768,39 +3819,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3823,39 +3874,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3876,53 +3927,6 @@
  Partita IVA n. LU 20260743.
  Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
  SPC-EUAmazon-1301823410754995</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Balance Paid on Your Selling on Amazon payment account</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
- We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
- Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
- To view your payment activity anytime, please log in to your account and refer the Payments Report page.
- Thank you for selling on Amazon.
- Amazon Payments UK Limited
-Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
- Was this e-mail helpful?
- SPC-EUAmaz</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5593,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5604,73 +5608,21 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
+          <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Reactivate your EU listings - GPSR compliance required</t>
+          <t>Amazon Review Rating Deals</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Reactivate your EU listings - GPSR compliance required
- Hello Weihai EU,
- Some of your listings have been deactivated from our European Union (EU) stores due to missing compliance information. This action does not impact your account health.
- You can find examples of your deactivated listings at the bottom of this email, and the full list on your Account Health page. Review the affected listings and next steps to meet General Product Safety Regulation (GPSR) requirements below.
- Submit compliance information
- Submit compliance information
- How do I reactivate my listings?
- To reactivate your listings, provide the required GPSR compliance information by following the instructions below:
--
- Go to your Account Health page .
-- Select 'Add filters' and check 'Listing removed' in the "Filter by action taken" column.
-- Click 'Submit' next to the deactivated listing and follow the instructions provided.
-- Follow the steps on Suppressed listings to resolve any outstanding listing issues. Existing issues prevent listings from being reactivated, even if you’ve fulfilled all compliance requirements.
- Note: If you’ve recently submitted information on your Account Health page, and no longer </t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 15:27:47 +0600</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Review Rating Deals</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -5696,40 +5648,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5745,40 +5697,40 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5794,39 +5746,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5842,39 +5794,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5890,39 +5842,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5938,39 +5890,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5984,39 +5936,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6034,40 +5986,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6083,39 +6035,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6131,39 +6083,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6179,40 +6131,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6228,39 +6180,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6277,39 +6229,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6338,39 +6290,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6386,39 +6338,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6432,39 +6384,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6479,39 +6431,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6531,39 +6483,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -6592,40 +6544,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -6638,39 +6590,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -6685,39 +6637,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -6730,40 +6682,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -6778,40 +6730,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -6825,39 +6777,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -6871,39 +6823,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -6918,39 +6870,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -6964,39 +6916,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -7011,39 +6963,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7058,39 +7010,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7109,39 +7061,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7157,39 +7109,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7210,39 +7162,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7260,40 +7212,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7311,39 +7263,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7360,39 +7312,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7410,40 +7362,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7461,39 +7413,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7511,39 +7463,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7560,39 +7512,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7607,39 +7559,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7658,39 +7610,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -7708,39 +7660,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -7779,39 +7731,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7827,40 +7779,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7876,39 +7828,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7924,39 +7876,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7970,40 +7922,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -8019,39 +7971,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8067,39 +8019,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8120,39 +8072,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8167,39 +8119,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -8216,39 +8168,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8262,39 +8214,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -8313,40 +8265,40 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -8360,40 +8312,40 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -8411,39 +8363,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -8476,39 +8428,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -8523,39 +8475,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -8574,226 +8526,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>96
- Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
- Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
- Inviare le informazioni sulla conformità
- Inviare le informazioni sulla conformità
- Come faccio a riattivare le mie offerte?
- Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
--
- Vai alla pagina Stato dell'account .
-- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
-- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
-- Segui la procedura indi</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>96
- Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
- Hola:
- Con entrada en vigor el 1 de mayo de 2026, las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición. Con esta actualización, seguimos los estándares del sector y te proporcionamos más visibilidad sobre tus actividades de retirada y puesta de inventario a nuestra disposición.
- Este cambio sólo afecta al momento en que se te cobra. No hay cambios en las tarifas por retirada y puesta de inventario a disposición de Amazon. Antes, estas tarifas se cobraban una vez que se completaba toda la solicitud de retirada o puesta de inventario a disposición de Amazon.
- No es necesario que hagas nada. Este cambio se aplicará automáticamente a las nuevas solicitudes de retirada y puesta de inventario a disposición de Amazon creadas a partir del 1 de mayo.
- Para consultar los cargos por envío de las retiradas y puestas de inventario a nuestra disposición y</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>96
- Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
- Dzień dobry,
- od 1 maja 2026 r. opłaty za wycofanie i usunięcie w ramach usługi Realizacja przez Amazon (FBA) będą pobierane od każdej jednostki w momencie jej wycofania lub usunięcia. Aktualizacja jest zgodna ze standardami branżowymi i zapewnia większą przejrzystość działań związanych z wycofywaniem i usuwaniem zapasów.
- Zmiana dotyczy wyłącznie momentu pobrania opłaty. Stawki opłat za wycofanie i usunięcie zapasów pozostają bez zmian. Wcześniej opłaty były pobierane po zakończeniu realizacji całego zlecenia wycofania zapasów lub zlecenia usunięcia zapasów.
- Nie musisz podejmować żadnych działań. Zmiana zostanie automatycznie zastosowana do nowych zleceń wycofania zapasów i zleceń usunięcia zapasów utworzonych od 1 maja.
- Aby sprawdzić opłaty na poziomie przesyłki dotyczące wycofania i usunięcia zapasów oraz terminy wycofywania jednostek, przejdź na kartę Transakcje .
- Więcej informacji znajdziesz na stronie Aktualizacje opłat za wycofanie i usunięcie zapasów w ramach FBA .
- Zespół Amazon Europe
- Zgłoś problem z tym e-mailem
- Jeśli masz pytani</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>96
- Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
- Buongiorno,
- a partire dal 1° maggio 2026, le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno addebitate per unità nel momento in cui ciascuna unità viene rimossa o destinata ad altro uso. Questo aggiornamento è in linea con gli standard del settore e offre una maggiore visibilità sulle attività di rimozione e reimpiego di inventario.
- Questa modifica riguarda solo i casi in cui ti viene addebitato il costo. Le tariffe per gli ordini di rimozione e di reimpiego di inventario rimangono invariate. In precedenza, queste tariffe venivano addebitate una volta completato l'intero ordine di rimozione o di reimpiego di inventario.
- A questo proposito, non è richiesto alcun intervento da parte tua. Questa modifica verrà applicata automaticamente ai nuovi ordini di rimozione e di reimpiego di inventario creati a partire dal 1° maggio.
- Per consultare i costi di rimozione e reimpiego di inventario a livello di spedizione e verificare quando le unità veng</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8817,39 +8582,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8873,39 +8638,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8926,39 +8691,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8980,39 +8745,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9035,39 +8800,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9088,39 +8853,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9143,39 +8908,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9205,39 +8970,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9286,39 +9051,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9327,39 +9092,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -9375,39 +9140,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -9423,109 +9188,6 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal and disposal fees to be charged as units are processed</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>96
- FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
- Hello,
- Effective May 1, 2026, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
- This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
- No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
- To review your removal and disposal shipment level charges and when units are removed, go to Transaction view .
- For more information, go to FBA Removal and Disposal fee updates .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon EU S.à r.l.
-38 avenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal and disposal fees to be charged as units are processed</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>96
- FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
- Hello,
- Effective as of May 1, 2026, Fulfilment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time that each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
- This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
- No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
- To review your removal and disposal shipment-level charges and when units are removed, go to Transaction view .
- For more information, go to FBA removal and disposal fee updates .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon EU S.à</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
